--- a/task136/golden/feeder_upgrade_2029.xlsx
+++ b/task136/golden/feeder_upgrade_2029.xlsx
@@ -10,9 +10,8 @@
     <sheet name="Call" sheetId="1" r:id="rId1"/>
     <sheet name="Forecast" sheetId="2" r:id="rId2"/>
     <sheet name="Solar Streets" sheetId="3" r:id="rId3"/>
-    <sheet name="DER Register check" sheetId="4" r:id="rId4"/>
-    <sheet name="Battery storage" sheetId="5" r:id="rId5"/>
-    <sheet name="Notes" sheetId="6" r:id="rId6"/>
+    <sheet name="DER Register" sheetId="4" r:id="rId4"/>
+    <sheet name="Notes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Forecast'!$3:$3</definedName>
@@ -27,9 +26,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="93">
-  <si>
-    <t>YRB24 takes the FY2027-28 hosting-capacity augmentation: its rooftop PV sits furthest above hosting capacity at the 31 August 2029 design point</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
+  <si>
+    <t>YRB27 takes the FY2027-28 hosting-capacity augmentation: its rooftop PV sits furthest above hosting capacity at the 31 August 2029 design point</t>
   </si>
   <si>
     <t>Yarrabin 22 kV feeders, forecast under NPP-114 rev 3 from a base date of 31 August 2026.</t>
@@ -38,75 +37,78 @@
     <t>Feeder to receive the augmentation</t>
   </si>
   <si>
+    <t>YRB27</t>
+  </si>
+  <si>
+    <t>Rooftop PV above hosting capacity at 31 August 2029 (MW)</t>
+  </si>
+  <si>
+    <t>Runner-up feeder</t>
+  </si>
+  <si>
     <t>YRB24</t>
   </si>
   <si>
-    <t>Rooftop PV above hosting capacity at 31 August 2029 (MW)</t>
-  </si>
-  <si>
-    <t>Runner-up feeder</t>
+    <t>Runner-up above hosting capacity (MW)</t>
+  </si>
+  <si>
+    <t>Gap between them (MW)</t>
+  </si>
+  <si>
+    <t>Solar Streets 2026, Bindarra Waters (YRB24): PV added (MW)</t>
+  </si>
+  <si>
+    <t>Solar Streets 2026, Wattleview (YRB27): PV added (MW)</t>
+  </si>
+  <si>
+    <t>YRB27's rooftop PV is forecast at 25.2 MW on 31 August 2029 against a 2029 hosting capacity of 23.30 MW; 1.7 MW of it is the Wattleview bulk-buy.</t>
+  </si>
+  <si>
+    <t>Past Solar Streets campaigns installed about 1.17 systems for every first application their suburb's owner-occupied houses lodged in the year before sign-ups opened (505 systems on 431 applications over the seven campaigns). That is the only basis on which the seven agree; per home letterboxed or per house without PV they vary several-fold (Solar Streets sheet).</t>
+  </si>
+  <si>
+    <t>Wattleview's owner-occupiers lodged 209 first applications in the year to August 2026 and Bindarra Waters' lodged 52, so Wattleview's campaign is expected to add about four times as much PV although Bindarra Waters has more houses still without it.</t>
+  </si>
+  <si>
+    <t>Forecast rooftop PV (micro EG) at 31 August 2029 by feeder</t>
+  </si>
+  <si>
+    <t>Feeder</t>
+  </si>
+  <si>
+    <t>Connected 31 Aug 2026 (kW)</t>
+  </si>
+  <si>
+    <t>Trend (kW a year, FY2023-24 to FY2025-26)</t>
+  </si>
+  <si>
+    <t>Base forecast 31 Aug 2029 (kW)</t>
+  </si>
+  <si>
+    <t>Solar Streets 2026 systems</t>
+  </si>
+  <si>
+    <t>Program capacity (kW)</t>
+  </si>
+  <si>
+    <t>Forecast 31 Aug 2029 (kW)</t>
+  </si>
+  <si>
+    <t>Hosting capacity, 2029 case (MW)</t>
+  </si>
+  <si>
+    <t>Above hosting capacity (MW)</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>YRB21</t>
   </si>
   <si>
     <t>YRB22</t>
   </si>
   <si>
-    <t>Runner-up above hosting capacity (MW)</t>
-  </si>
-  <si>
-    <t>Gap between them (MW)</t>
-  </si>
-  <si>
-    <t>Solar Streets 2027, Bindarra Waters: systems added</t>
-  </si>
-  <si>
-    <t>Solar Streets 2027, Wattleview: systems added</t>
-  </si>
-  <si>
-    <t>YRB24's forecast rooftop PV at 31 August 2029 is 6.1 MW against a 2029 hosting capacity of 4.22 MW; most of the difference is the Bindarra Waters bulk-buy.</t>
-  </si>
-  <si>
-    <t>Each past Solar Streets campaign installed systems on 4.55 to 4.63 per cent of the owner-occupied houses in its suburb that had no PV when sign-ups opened (4.58 per cent over all seven); that is the rate carried to the 2027 campaigns.</t>
-  </si>
-  <si>
-    <t>Systems per home letterboxed varied much more from one campaign to the next, because the suburbs differed in how many of their addresses were units, rented houses or houses that already had panels.</t>
-  </si>
-  <si>
-    <t>Forecast rooftop PV (micro EG) at 31 August 2029 by feeder</t>
-  </si>
-  <si>
-    <t>Feeder</t>
-  </si>
-  <si>
-    <t>Connected 31 Aug 2026 (kW)</t>
-  </si>
-  <si>
-    <t>Trend (kW a year, FY2023-24 to FY2025-26)</t>
-  </si>
-  <si>
-    <t>Base forecast 31 Aug 2029 (kW)</t>
-  </si>
-  <si>
-    <t>Solar Streets 2027 systems</t>
-  </si>
-  <si>
-    <t>Program capacity (kW)</t>
-  </si>
-  <si>
-    <t>Forecast 31 Aug 2029 (kW)</t>
-  </si>
-  <si>
-    <t>Hosting capacity, 2029 case (MW)</t>
-  </si>
-  <si>
-    <t>Above hosting capacity (MW)</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>YRB21</t>
-  </si>
-  <si>
     <t>YRB23</t>
   </si>
   <si>
@@ -116,19 +118,16 @@
     <t>YRB26</t>
   </si>
   <si>
-    <t>YRB27</t>
-  </si>
-  <si>
     <t>YRB28</t>
   </si>
   <si>
     <t>Yarrabin</t>
   </si>
   <si>
-    <t>Connected capacity: each NMI's latest connected configuration on the network model's feeder; trend: the yearly increase in connected capacity less program systems first connected that year; program systems at the feeder's FY2025-26 average inverter rating (NPP-114 3.2, 4.1, 4.2).</t>
-  </si>
-  <si>
-    <t>Solar Streets: systems per owner-occupied house without PV when sign-ups opened</t>
+    <t>Connected capacity: each NMI's latest connected configuration on the network model's feeder; trend: the yearly increase in connected capacity less program systems first connected that year; program systems at the feeder's FY2025-26 average inverter rating (NPP-114 3.2, 4.1 to 4.3). Systems are carried unrounded.</t>
+  </si>
+  <si>
+    <t>Solar Streets: what a campaign installs, carried from the seven past campaigns</t>
   </si>
   <si>
     <t>Campaign</t>
@@ -140,13 +139,13 @@
     <t>Sign-ups opened</t>
   </si>
   <si>
-    <t>Owner-occupied houses without PV at opening</t>
-  </si>
-  <si>
-    <t>Systems installed</t>
-  </si>
-  <si>
-    <t>Systems per such house (%)</t>
+    <t>First applications from owner-occupied houses, 12 months before sign-ups opened</t>
+  </si>
+  <si>
+    <t>Systems installed (program reference)</t>
+  </si>
+  <si>
+    <t>Systems per first application</t>
   </si>
   <si>
     <t>GLM18</t>
@@ -194,19 +193,40 @@
     <t>All seven</t>
   </si>
   <si>
-    <t>2027 campaign</t>
+    <t>Basis tried</t>
+  </si>
+  <si>
+    <t>Pooled rate over the seven</t>
+  </si>
+  <si>
+    <t>Lowest campaign</t>
+  </si>
+  <si>
+    <t>Highest campaign</t>
+  </si>
+  <si>
+    <t>Coefficient of variation</t>
+  </si>
+  <si>
+    <t>Per 100 homes letterboxed (the council's participation rate)</t>
+  </si>
+  <si>
+    <t>Per 100 owner-occupied houses in the suburb</t>
+  </si>
+  <si>
+    <t>Per 100 owner-occupied houses without PV when sign-ups opened</t>
+  </si>
+  <si>
+    <t>Per first application from the suburb's owner-occupied houses in the 12 months before sign-ups opened</t>
+  </si>
+  <si>
+    <t>2026 campaign</t>
   </si>
   <si>
     <t>Sign-ups open</t>
   </si>
   <si>
-    <t>Owner-occupied houses without PV, 31 Aug 2026</t>
-  </si>
-  <si>
-    <t>Less first applications from such houses in FY2025-26</t>
-  </si>
-  <si>
-    <t>Expected without PV at opening</t>
+    <t>First applications from owner-occupied houses, 1 Sep 2025 to 31 Aug 2026</t>
   </si>
   <si>
     <t>Systems added</t>
@@ -215,40 +235,43 @@
     <t>Average inverter (kW, FY2025-26)</t>
   </si>
   <si>
-    <t>Capacity added (kW)</t>
-  </si>
-  <si>
-    <t>BDW27</t>
+    <t>PV added (MW)</t>
+  </si>
+  <si>
+    <t>BDW26</t>
   </si>
   <si>
     <t>Bindarra Waters</t>
   </si>
   <si>
-    <t>WTV27</t>
+    <t>WTV26</t>
   </si>
   <si>
     <t>Wattleview</t>
   </si>
   <si>
-    <t>Connected micro EG at 31 August 2026 against the DER Register extract of 5 September 2026</t>
-  </si>
-  <si>
-    <t>Connected systems not shown on the DER Register</t>
-  </si>
-  <si>
-    <t>Active DER Register sites with no connected system</t>
-  </si>
-  <si>
-    <t>Matched by NMI (ten characters); registrations lodged against a builder's temporary supply NMI are read at the permanent NMI from the re-allocation log.</t>
-  </si>
-  <si>
-    <t>Battery storage at active DER Register sites, 5 September 2026</t>
+    <t>Owner-occupied house: rates roll land use 02 with rating R1, matched to NMIs through the GIS cross-reference. A first application is the earliest application at the NMI, other than a withdrawn one. Systems installed are the connected new systems lodged with the campaign's reference.</t>
+  </si>
+  <si>
+    <t>Active DER Register sites by feeder, extract as at 31 August 2026</t>
+  </si>
+  <si>
+    <t>Active sites</t>
+  </si>
+  <si>
+    <t>Sites first lodged in FY2025-26</t>
+  </si>
+  <si>
+    <t>Inverter capacity (kW)</t>
   </si>
   <si>
     <t>Battery storage (kWh)</t>
   </si>
   <si>
-    <t>Each active AC connection's storage counted once (the extract repeats it on every battery module row); decommissioned connections excluded. Rounded to the nearest 10 kWh by feeder and in total.</t>
+    <t>A site is the premises' NMI (ten characters; a builder's temporary supply NMI read at the NMI that replaced it), placed on the feeder the network model shows supplying it at 31 August 2026. First lodged: the earliest registration of any AC connection at the site, decommissioned ones included.</t>
+  </si>
+  <si>
+    <t>Inverter capacity: two-inverter connections lodged on the installer portal before July 2024 carry the connection's total on each inverter row and are counted once. Battery storage: Sungrow SBR stacks carry the stack's total on each module row and are counted once; other modular batteries are lodged module by module and summed. Rounded to the nearest 10 kW and 10 kWh.</t>
   </si>
   <si>
     <t>Notes and sources</t>
@@ -278,43 +301,38 @@
     <t>Buchanan Power Engineering report BPE-2026-031 (24 July 2026), spring 2029 minimum-demand case (clause 5.1).</t>
   </si>
   <si>
-    <t>Solar Streets 2027</t>
-  </si>
-  <si>
-    <t>Merindah City Council letter of 14 August 2026 (reference SS/2027/01): sign-ups 6 September to 26 November 2027 in Bindarra Waters and Wattleview.</t>
+    <t>Solar Streets 2026</t>
+  </si>
+  <si>
+    <t>Merindah City Council letter of 14 August 2026 (reference SS/2026/02): sign-ups 1 September to 27 November 2026 in Bindarra Waters and Wattleview.</t>
   </si>
   <si>
     <t>Past campaigns</t>
   </si>
   <si>
-    <t>The council's Solar Streets summary, 2018 to 2024, for sign-up dates; systems counted from program references in the connection register, which agree with the council's systems installed for every campaign.</t>
-  </si>
-  <si>
-    <t>Owner-occupied house</t>
-  </si>
-  <si>
-    <t>Rates roll land use code 02 (single unit dwelling) with rating category R1, matched to NMIs through the GIS cross-reference; without PV when no application at any of its NMIs, other than a withdrawn one, was received before the date.</t>
+    <t>The council's Solar Streets summary, 2018 to 2024, for sign-up dates; systems counted from program references in the connection register, which agree with the council's systems installed for every campaign. The rate is pooled over the seven (clause 4.2).</t>
   </si>
   <si>
     <t>DER Register</t>
   </si>
   <si>
-    <t>Extract of 5 September 2026, AC connections and devices for NMIs on the Yarrabin feeders.</t>
+    <t>Extract as at 31 August 2026, AC connections and devices at NMIs on the Yarrabin feeders; the NMI re-allocation log for builders' temporary supply NMIs.</t>
   </si>
   <si>
     <t>Rounding</t>
   </si>
   <si>
-    <t>Carried unrounded and rounded once: MW to one decimal and systems to the nearest ten (clause 7.1); battery storage to the nearest 10 kWh.</t>
+    <t>Carried unrounded and rounded once: MW to one decimal (clause 7.1); inverter capacity to the nearest 10 kW and battery storage to the nearest 10 kWh.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="d mmm yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -404,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -414,20 +432,20 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -739,7 +757,7 @@
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="60.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -782,7 +800,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -790,37 +808,37 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5">
-        <v>240</v>
+      <c r="B9" s="4">
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="5">
-        <v>30</v>
+      <c r="B10" s="4">
+        <v>1.7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -850,39 +868,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
@@ -890,23 +908,24 @@
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="9">
-        <v>16136</v>
-      </c>
-      <c r="C4" s="9">
-        <v>928</v>
-      </c>
-      <c r="D4" s="9">
-        <v>18920</v>
-      </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9">
-        <v>18920</v>
+      <c r="B4" s="8">
+        <v>13600</v>
+      </c>
+      <c r="C4" s="8">
+        <v>776</v>
+      </c>
+      <c r="D4" s="8">
+        <v>15928</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8">
+        <v>15928</v>
       </c>
       <c r="H4" s="10">
-        <v>17.81</v>
-      </c>
-      <c r="I4" s="11">
+        <v>14.82</v>
+      </c>
+      <c r="I4" s="9">
         <v>1.1</v>
       </c>
       <c r="J4">
@@ -915,52 +934,54 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="9">
-        <v>13690</v>
-      </c>
-      <c r="C5" s="9">
-        <v>826</v>
-      </c>
-      <c r="D5" s="9">
-        <v>16168</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9">
-        <v>16168</v>
+        <v>26</v>
+      </c>
+      <c r="B5" s="8">
+        <v>20336</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1054</v>
+      </c>
+      <c r="D5" s="8">
+        <v>23499</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8">
+        <v>23499</v>
       </c>
       <c r="H5" s="10">
-        <v>14.66</v>
-      </c>
-      <c r="I5" s="11">
-        <v>1.5</v>
+        <v>22.29</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1.2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="9">
-        <v>10742</v>
-      </c>
-      <c r="C6" s="9">
-        <v>576</v>
-      </c>
-      <c r="D6" s="9">
-        <v>12468</v>
-      </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9">
-        <v>12468</v>
+        <v>27</v>
+      </c>
+      <c r="B6" s="8">
+        <v>10662</v>
+      </c>
+      <c r="C6" s="8">
+        <v>498</v>
+      </c>
+      <c r="D6" s="8">
+        <v>12157</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8">
+        <v>12157</v>
       </c>
       <c r="H6" s="10">
-        <v>12.03</v>
-      </c>
-      <c r="I6" s="11">
+        <v>11.72</v>
+      </c>
+      <c r="I6" s="9">
         <v>0.4</v>
       </c>
       <c r="J6">
@@ -969,84 +990,86 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9">
-        <v>3064</v>
-      </c>
-      <c r="C7" s="9">
-        <v>432</v>
-      </c>
-      <c r="D7" s="9">
-        <v>4360</v>
-      </c>
-      <c r="E7">
-        <v>240</v>
-      </c>
-      <c r="F7" s="9">
-        <v>1752</v>
-      </c>
-      <c r="G7" s="9">
-        <v>6112</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="8">
+        <v>4637</v>
+      </c>
+      <c r="C7" s="8">
+        <v>498</v>
+      </c>
+      <c r="D7" s="8">
+        <v>6130</v>
+      </c>
+      <c r="E7" s="9">
+        <v>60.9</v>
+      </c>
+      <c r="F7" s="8">
+        <v>396</v>
+      </c>
+      <c r="G7" s="8">
+        <v>6525</v>
       </c>
       <c r="H7" s="10">
-        <v>4.22</v>
-      </c>
-      <c r="I7" s="11">
-        <v>1.9</v>
+        <v>5.13</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1.4</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="9">
-        <v>6459</v>
-      </c>
-      <c r="C8" s="9">
-        <v>510</v>
-      </c>
-      <c r="D8" s="9">
-        <v>7988</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9">
-        <v>7988</v>
+        <v>28</v>
+      </c>
+      <c r="B8" s="8">
+        <v>4733</v>
+      </c>
+      <c r="C8" s="8">
+        <v>372</v>
+      </c>
+      <c r="D8" s="8">
+        <v>5851</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8">
+        <v>5851</v>
       </c>
       <c r="H8" s="10">
-        <v>6.75</v>
-      </c>
-      <c r="I8" s="11">
-        <v>1.2</v>
+        <v>4.79</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1.1</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="9">
-        <v>11984</v>
-      </c>
-      <c r="C9" s="9">
-        <v>690</v>
-      </c>
-      <c r="D9" s="9">
-        <v>14053</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9">
-        <v>14053</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="8">
+        <v>10370</v>
+      </c>
+      <c r="C9" s="8">
+        <v>504</v>
+      </c>
+      <c r="D9" s="8">
+        <v>11884</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8">
+        <v>11884</v>
       </c>
       <c r="H9" s="10">
-        <v>14.71</v>
-      </c>
-      <c r="I9" s="11">
+        <v>12.54</v>
+      </c>
+      <c r="I9" s="9">
         <v>-0.7</v>
       </c>
       <c r="J9">
@@ -1055,57 +1078,58 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="9">
-        <v>12540</v>
-      </c>
-      <c r="C10" s="9">
-        <v>754</v>
-      </c>
-      <c r="D10" s="9">
-        <v>14803</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10" s="9">
-        <v>204</v>
-      </c>
-      <c r="G10" s="9">
-        <v>15007</v>
+        <v>3</v>
+      </c>
+      <c r="B10" s="8">
+        <v>17938</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1852</v>
+      </c>
+      <c r="D10" s="8">
+        <v>23495</v>
+      </c>
+      <c r="E10" s="9">
+        <v>244.9</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1707</v>
+      </c>
+      <c r="G10" s="8">
+        <v>25202</v>
       </c>
       <c r="H10" s="10">
-        <v>13.99</v>
-      </c>
-      <c r="I10" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="J10">
         <v>1</v>
-      </c>
-      <c r="J10">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="9">
-        <v>10567</v>
-      </c>
-      <c r="C11" s="9">
-        <v>563</v>
-      </c>
-      <c r="D11" s="9">
-        <v>12257</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9">
-        <v>12257</v>
+      <c r="B11" s="8">
+        <v>10078</v>
+      </c>
+      <c r="C11" s="8">
+        <v>540</v>
+      </c>
+      <c r="D11" s="8">
+        <v>11698</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8">
+        <v>11698</v>
       </c>
       <c r="H11" s="10">
-        <v>11.54</v>
-      </c>
-      <c r="I11" s="11">
+        <v>10.99</v>
+      </c>
+      <c r="I11" s="9">
         <v>0.7</v>
       </c>
       <c r="J11">
@@ -1113,26 +1137,26 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="13">
-        <v>85181</v>
-      </c>
-      <c r="C12" s="13">
-        <v>5279</v>
-      </c>
-      <c r="D12" s="13">
-        <v>101018</v>
+      <c r="B12" s="12">
+        <v>92355</v>
+      </c>
+      <c r="C12" s="12">
+        <v>6096</v>
+      </c>
+      <c r="D12" s="12">
+        <v>110642</v>
       </c>
       <c r="E12" s="13">
-        <v>270</v>
-      </c>
-      <c r="F12" s="13">
-        <v>1956</v>
-      </c>
-      <c r="G12" s="13">
-        <v>102974</v>
+        <v>305.8</v>
+      </c>
+      <c r="F12" s="12">
+        <v>2103</v>
+      </c>
+      <c r="G12" s="12">
+        <v>112744</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1148,50 +1172,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD1995C-42C9-513D-861B-8743FF29CB14}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1204,17 +1226,17 @@
       <c r="D4" s="14">
         <v>43346</v>
       </c>
-      <c r="E4" s="9">
-        <v>740</v>
+      <c r="E4">
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G4" s="10">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1222,22 +1244,22 @@
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D5" s="14">
         <v>43710</v>
       </c>
-      <c r="E5" s="9">
-        <v>1054</v>
+      <c r="E5">
+        <v>162</v>
       </c>
       <c r="F5">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="G5" s="10">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1245,22 +1267,22 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="14">
         <v>44445</v>
       </c>
-      <c r="E6" s="9">
-        <v>2270</v>
+      <c r="E6">
+        <v>43</v>
       </c>
       <c r="F6">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="G6" s="10">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -1268,22 +1290,22 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="14">
         <v>44627</v>
       </c>
-      <c r="E7" s="9">
-        <v>810</v>
+      <c r="E7">
+        <v>81</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="G7" s="10">
-        <v>4.57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1296,17 +1318,17 @@
       <c r="D8" s="14">
         <v>44809</v>
       </c>
-      <c r="E8" s="9">
-        <v>885</v>
+      <c r="E8">
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G8" s="10">
-        <v>4.63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1314,22 +1336,22 @@
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="14">
         <v>45173</v>
       </c>
-      <c r="E9" s="9">
-        <v>1207</v>
+      <c r="E9">
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G9" s="10">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -1342,124 +1364,199 @@
       <c r="D10" s="14">
         <v>45537</v>
       </c>
-      <c r="E10" s="9">
-        <v>851</v>
+      <c r="E10">
+        <v>55</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G10" s="10">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="9">
-        <v>7817</v>
-      </c>
-      <c r="F11">
-        <v>358</v>
-      </c>
-      <c r="G11" s="10">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="44" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="E11" s="11">
+        <v>431</v>
+      </c>
+      <c r="F11" s="11">
+        <v>505</v>
+      </c>
+      <c r="G11" s="15">
+        <v>1.172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.94</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G14" s="10">
+        <v>4.38</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="10">
+        <v>3.34</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="G15" s="10">
+        <v>5.98</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="10">
+        <v>6.1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>2.33</v>
+      </c>
+      <c r="G16" s="10">
+        <v>13.9</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="16">
+        <v>1.172</v>
+      </c>
+      <c r="F17" s="16">
+        <v>1.03</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1.346</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14">
+        <v>46266</v>
+      </c>
+      <c r="E20">
+        <v>52</v>
+      </c>
+      <c r="F20" s="9">
+        <v>60.9</v>
+      </c>
+      <c r="G20" s="10">
+        <v>6.5</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="14">
-        <v>46636</v>
-      </c>
-      <c r="E14" s="9">
-        <v>5299</v>
-      </c>
-      <c r="F14">
-        <v>24</v>
-      </c>
-      <c r="G14" s="9">
-        <v>5275</v>
-      </c>
-      <c r="H14">
-        <v>240</v>
-      </c>
-      <c r="I14" s="10">
-        <v>7.25</v>
-      </c>
-      <c r="J14" s="9">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="14">
-        <v>46636</v>
-      </c>
-      <c r="E15" s="9">
-        <v>720</v>
-      </c>
-      <c r="F15">
-        <v>52</v>
-      </c>
-      <c r="G15" s="9">
-        <v>668</v>
-      </c>
-      <c r="H15">
-        <v>30</v>
-      </c>
-      <c r="I15" s="10">
-        <v>6.67</v>
-      </c>
-      <c r="J15" s="9">
-        <v>204</v>
+      <c r="D21" s="14">
+        <v>46266</v>
+      </c>
+      <c r="E21">
+        <v>209</v>
+      </c>
+      <c r="F21" s="9">
+        <v>244.9</v>
+      </c>
+      <c r="G21" s="10">
+        <v>6.97</v>
+      </c>
+      <c r="H21" s="9">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1468,133 +1565,183 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E09FB9-8283-5F11-849F-34440BE0D960}">
-  <dimension ref="A1:C14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D24055-7B73-5E2C-A2FC-EC8135CC5735}">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="8">
+        <v>2323</v>
+      </c>
+      <c r="C4" s="8">
+        <v>82</v>
+      </c>
+      <c r="D4" s="8">
+        <v>14000</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="8">
+        <v>3448</v>
+      </c>
+      <c r="C5" s="8">
+        <v>130</v>
+      </c>
+      <c r="D5" s="8">
+        <v>20680</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8">
+        <v>1713</v>
+      </c>
+      <c r="C6" s="8">
+        <v>65</v>
+      </c>
+      <c r="D6" s="8">
+        <v>10860</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" s="8">
+        <v>702</v>
+      </c>
+      <c r="C7" s="8">
+        <v>68</v>
+      </c>
+      <c r="D7" s="8">
+        <v>4730</v>
+      </c>
+      <c r="E7" s="8">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8">
+        <v>717</v>
+      </c>
+      <c r="C8" s="8">
+        <v>44</v>
+      </c>
+      <c r="D8" s="8">
+        <v>4850</v>
+      </c>
+      <c r="E8" s="8">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1996</v>
+      </c>
+      <c r="C9" s="8">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8">
+        <v>10830</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="8">
+        <v>2729</v>
+      </c>
+      <c r="C10" s="8">
+        <v>252</v>
+      </c>
+      <c r="D10" s="8">
+        <v>18040</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="12">
-        <v>79</v>
-      </c>
-      <c r="C12" s="12">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="8">
+        <v>1781</v>
+      </c>
+      <c r="C11" s="8">
+        <v>62</v>
+      </c>
+      <c r="D11" s="8">
+        <v>10340</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1603,112 +1750,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7764B8B4-77CB-53A9-809C-4BD18E483FC4}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="44" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="9">
-        <v>2440</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="9">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="9">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="9">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="9">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="13">
-        <v>11940</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71292A8F-0BD8-598F-BC7E-D7C6F65ED072}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -1716,80 +1759,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>74</v>
+      <c r="A1" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>76</v>
+      <c r="A3" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>78</v>
+      <c r="A4" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>80</v>
+      <c r="A5" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>82</v>
+      <c r="A6" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>84</v>
+      <c r="A7" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>86</v>
+      <c r="A8" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>88</v>
+      <c r="A9" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>92</v>
+      <c r="A10" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/task136/golden/feeder_upgrade_2029.xlsx
+++ b/task136/golden/feeder_upgrade_2029.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
   <si>
     <t>YRB27 takes the FY2027-28 hosting-capacity augmentation: its rooftop PV sits furthest above hosting capacity at the 31 August 2029 design point</t>
   </si>
@@ -55,19 +55,19 @@
     <t>Gap between them (MW)</t>
   </si>
   <si>
-    <t>Solar Streets 2026, Bindarra Waters (YRB24): PV added (MW)</t>
-  </si>
-  <si>
-    <t>Solar Streets 2026, Wattleview (YRB27): PV added (MW)</t>
-  </si>
-  <si>
-    <t>YRB27's rooftop PV is forecast at 25.2 MW on 31 August 2029 against a 2029 hosting capacity of 23.30 MW; 1.7 MW of it is the Wattleview bulk-buy.</t>
-  </si>
-  <si>
-    <t>Past Solar Streets campaigns installed about 1.17 systems for every first application their suburb's owner-occupied houses lodged in the year before sign-ups opened (505 systems on 431 applications over the seven campaigns). That is the only basis on which the seven agree; per home letterboxed or per house without PV they vary several-fold (Solar Streets sheet).</t>
-  </si>
-  <si>
-    <t>Wattleview's owner-occupiers lodged 209 first applications in the year to August 2026 and Bindarra Waters' lodged 52, so Wattleview's campaign is expected to add about four times as much PV although Bindarra Waters has more houses still without it.</t>
+    <t>Solar Streets 2026, Bindarra Waters (YRB24): PV added by 31 Aug 2029 (MW)</t>
+  </si>
+  <si>
+    <t>Solar Streets 2026, Wattleview (YRB27): PV added by 31 Aug 2029 (MW)</t>
+  </si>
+  <si>
+    <t>YRB27 forecast 16.1 MW at 31 Aug 2029 against 2029 hosting capacity 14.19 MW; 0.7 MW of it is the Wattleview bulk-buy.</t>
+  </si>
+  <si>
+    <t>Bulk-buys counted at what they add by the design point, not systems installed. The seven past campaigns installed 9.32 systems per 100 houses without PV, but more than half of those households would have gone solar within three years anyway; read against suburbs whose campaign had not yet run, they added 4.09 per 100 (Solar Streets tab).</t>
+  </si>
+  <si>
+    <t>Installed-systems basis puts YRB24 first. On the added basis Bindarra Waters (4,537 houses without PV) adds 1.7 MW and YRB24 stays 0.2 MW short of YRB27.</t>
   </si>
   <si>
     <t>Forecast rooftop PV (micro EG) at 31 August 2029 by feeder</t>
@@ -85,10 +85,10 @@
     <t>Base forecast 31 Aug 2029 (kW)</t>
   </si>
   <si>
-    <t>Solar Streets 2026 systems</t>
-  </si>
-  <si>
-    <t>Program capacity (kW)</t>
+    <t>Systems the 2026 bulk-buy adds</t>
+  </si>
+  <si>
+    <t>Bulk-buy addition (kW)</t>
   </si>
   <si>
     <t>Forecast 31 Aug 2029 (kW)</t>
@@ -124,10 +124,10 @@
     <t>Yarrabin</t>
   </si>
   <si>
-    <t>Connected capacity: each NMI's latest connected configuration on the network model's feeder; trend: the yearly increase in connected capacity less program systems first connected that year; program systems at the feeder's FY2025-26 average inverter rating (NPP-114 3.2, 4.1 to 4.3). Systems are carried unrounded.</t>
-  </si>
-  <si>
-    <t>Solar Streets: what a campaign installs, carried from the seven past campaigns</t>
+    <t>Connected capacity: each NMI's latest connected configuration on the network model's feeder. Trend: yearly increase in connected capacity less program systems first connected that year (NPP-114 3.2). Bulk-buy addition: systems the campaign adds by 31 Aug 2029 at the feeder's FY2025-26 average new inverter (4.1, 4.3). Carried unrounded.</t>
+  </si>
+  <si>
+    <t>Solar Streets: systems installed against systems added, seven past campaigns</t>
   </si>
   <si>
     <t>Campaign</t>
@@ -139,13 +139,31 @@
     <t>Sign-ups opened</t>
   </si>
   <si>
-    <t>First applications from owner-occupied houses, 12 months before sign-ups opened</t>
-  </si>
-  <si>
-    <t>Systems installed (program reference)</t>
-  </si>
-  <si>
-    <t>Systems per first application</t>
+    <t>Window to</t>
+  </si>
+  <si>
+    <t>Owner-occupied houses without PV at opening</t>
+  </si>
+  <si>
+    <t>Systems installed (program ref)</t>
+  </si>
+  <si>
+    <t>First applications, 12 months before</t>
+  </si>
+  <si>
+    <t>First applications in window (all, incl. program)</t>
+  </si>
+  <si>
+    <t>Comparison suburbs: window / 12 months before</t>
+  </si>
+  <si>
+    <t>Expected in window without campaign</t>
+  </si>
+  <si>
+    <t>Added by campaign</t>
+  </si>
+  <si>
+    <t>Added per 100 houses without PV</t>
   </si>
   <si>
     <t>GLM18</t>
@@ -193,31 +211,7 @@
     <t>All seven</t>
   </si>
   <si>
-    <t>Basis tried</t>
-  </si>
-  <si>
-    <t>Pooled rate over the seven</t>
-  </si>
-  <si>
-    <t>Lowest campaign</t>
-  </si>
-  <si>
-    <t>Highest campaign</t>
-  </si>
-  <si>
-    <t>Coefficient of variation</t>
-  </si>
-  <si>
-    <t>Per 100 homes letterboxed (the council's participation rate)</t>
-  </si>
-  <si>
-    <t>Per 100 owner-occupied houses in the suburb</t>
-  </si>
-  <si>
-    <t>Per 100 owner-occupied houses without PV when sign-ups opened</t>
-  </si>
-  <si>
-    <t>Per first application from the suburb's owner-occupied houses in the 12 months before sign-ups opened</t>
+    <t>Installed per 100 houses without PV, all seven: 9.32</t>
   </si>
   <si>
     <t>2026 campaign</t>
@@ -226,13 +220,13 @@
     <t>Sign-ups open</t>
   </si>
   <si>
-    <t>First applications from owner-occupied houses, 1 Sep 2025 to 31 Aug 2026</t>
-  </si>
-  <si>
-    <t>Systems added</t>
-  </si>
-  <si>
-    <t>Average inverter (kW, FY2025-26)</t>
+    <t>Owner-occupied houses without PV, 1 Sep 2026</t>
+  </si>
+  <si>
+    <t>Systems added by 31 Aug 2029</t>
+  </si>
+  <si>
+    <t>Average new inverter (kW, FY2025-26)</t>
   </si>
   <si>
     <t>PV added (MW)</t>
@@ -250,7 +244,7 @@
     <t>Wattleview</t>
   </si>
   <si>
-    <t>Owner-occupied house: rates roll land use 02 with rating R1, matched to NMIs through the GIS cross-reference. A first application is the earliest application at the NMI, other than a withdrawn one. Systems installed are the connected new systems lodged with the campaign's reference.</t>
+    <t>Owner-occupied house: rates roll land use 02, rating R1, matched to NMIs via the GIS cross-reference. First application: earliest application at the house other than a withdrawn one, by received date. Window: 36 months from sign-ups opening, or to 31 Aug 2026 for BNR23 and PBG24. Comparison: suburbs whose own campaign opens after the window (not yet treated). Expected without campaign = suburb's first applications in the 12 months before x comparison suburbs' window / 12-month ratio.</t>
   </si>
   <si>
     <t>Active DER Register sites by feeder, extract as at 31 August 2026</t>
@@ -310,7 +304,7 @@
     <t>Past campaigns</t>
   </si>
   <si>
-    <t>The council's Solar Streets summary, 2018 to 2024, for sign-up dates; systems counted from program references in the connection register, which agree with the council's systems installed for every campaign. The rate is pooled over the seven (clause 4.2).</t>
+    <t>Council Solar Streets summary 2018 to 2024 for sign-up dates; systems from program references in the connection register, which match the council's systems installed. What each campaign added is read against suburbs whose campaign had not yet run over the same months.</t>
   </si>
   <si>
     <t>DER Register</t>
@@ -329,10 +323,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="d mmm yyyy"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -422,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -444,8 +439,10 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -800,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -808,7 +805,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -816,7 +813,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -824,7 +821,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="4">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -909,27 +906,27 @@
         <v>25</v>
       </c>
       <c r="B4" s="8">
-        <v>13600</v>
+        <v>18706</v>
       </c>
       <c r="C4" s="8">
-        <v>776</v>
+        <v>1098</v>
       </c>
       <c r="D4" s="8">
-        <v>15928</v>
+        <v>21998</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8">
-        <v>15928</v>
+        <v>21998</v>
       </c>
       <c r="H4" s="10">
-        <v>14.82</v>
+        <v>21.14</v>
       </c>
       <c r="I4" s="9">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -937,24 +934,24 @@
         <v>26</v>
       </c>
       <c r="B5" s="8">
-        <v>20336</v>
+        <v>18531</v>
       </c>
       <c r="C5" s="8">
-        <v>1054</v>
+        <v>1551</v>
       </c>
       <c r="D5" s="8">
-        <v>23499</v>
+        <v>23185</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8">
-        <v>23499</v>
+        <v>23185</v>
       </c>
       <c r="H5" s="10">
-        <v>22.29</v>
+        <v>21.79</v>
       </c>
       <c r="I5" s="9">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -965,21 +962,21 @@
         <v>27</v>
       </c>
       <c r="B6" s="8">
-        <v>10662</v>
+        <v>11954</v>
       </c>
       <c r="C6" s="8">
-        <v>498</v>
+        <v>810</v>
       </c>
       <c r="D6" s="8">
-        <v>12157</v>
+        <v>14385</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8">
-        <v>12157</v>
+        <v>14385</v>
       </c>
       <c r="H6" s="10">
-        <v>11.72</v>
+        <v>13.95</v>
       </c>
       <c r="I6" s="9">
         <v>0.4</v>
@@ -993,28 +990,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="8">
-        <v>4637</v>
+        <v>17845</v>
       </c>
       <c r="C7" s="8">
-        <v>498</v>
+        <v>1935</v>
       </c>
       <c r="D7" s="8">
-        <v>6130</v>
+        <v>23648</v>
       </c>
       <c r="E7" s="9">
-        <v>60.9</v>
+        <v>185.6</v>
       </c>
       <c r="F7" s="8">
-        <v>396</v>
+        <v>1698</v>
       </c>
       <c r="G7" s="8">
-        <v>6525</v>
+        <v>25346</v>
       </c>
       <c r="H7" s="10">
-        <v>5.13</v>
+        <v>23.65</v>
       </c>
       <c r="I7" s="9">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -1025,27 +1022,27 @@
         <v>28</v>
       </c>
       <c r="B8" s="8">
-        <v>4733</v>
+        <v>21255</v>
       </c>
       <c r="C8" s="8">
-        <v>372</v>
+        <v>1736</v>
       </c>
       <c r="D8" s="8">
-        <v>5851</v>
+        <v>26462</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8">
-        <v>5851</v>
+        <v>26462</v>
       </c>
       <c r="H8" s="10">
-        <v>4.79</v>
+        <v>25.49</v>
       </c>
       <c r="I8" s="9">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1053,21 +1050,21 @@
         <v>29</v>
       </c>
       <c r="B9" s="8">
-        <v>10370</v>
+        <v>11808</v>
       </c>
       <c r="C9" s="8">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="D9" s="8">
-        <v>11884</v>
+        <v>13514</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8">
-        <v>11884</v>
+        <v>13514</v>
       </c>
       <c r="H9" s="10">
-        <v>12.54</v>
+        <v>14.17</v>
       </c>
       <c r="I9" s="9">
         <v>-0.7</v>
@@ -1081,25 +1078,25 @@
         <v>3</v>
       </c>
       <c r="B10" s="8">
-        <v>17938</v>
+        <v>11645</v>
       </c>
       <c r="C10" s="8">
-        <v>1852</v>
+        <v>1245</v>
       </c>
       <c r="D10" s="8">
-        <v>23495</v>
+        <v>15380</v>
       </c>
       <c r="E10" s="9">
-        <v>244.9</v>
+        <v>76</v>
       </c>
       <c r="F10" s="8">
-        <v>1707</v>
+        <v>710</v>
       </c>
       <c r="G10" s="8">
-        <v>25202</v>
+        <v>16090</v>
       </c>
       <c r="H10" s="10">
-        <v>23.3</v>
+        <v>14.19</v>
       </c>
       <c r="I10" s="9">
         <v>1.9</v>
@@ -1113,21 +1110,21 @@
         <v>30</v>
       </c>
       <c r="B11" s="8">
-        <v>10078</v>
+        <v>16554</v>
       </c>
       <c r="C11" s="8">
-        <v>540</v>
+        <v>1168</v>
       </c>
       <c r="D11" s="8">
-        <v>11698</v>
+        <v>20057</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8">
-        <v>11698</v>
+        <v>20057</v>
       </c>
       <c r="H11" s="10">
-        <v>10.99</v>
+        <v>19.34</v>
       </c>
       <c r="I11" s="9">
         <v>0.7</v>
@@ -1141,22 +1138,22 @@
         <v>31</v>
       </c>
       <c r="B12" s="12">
-        <v>92355</v>
+        <v>128297</v>
       </c>
       <c r="C12" s="12">
-        <v>6096</v>
+        <v>10111</v>
       </c>
       <c r="D12" s="12">
-        <v>110642</v>
+        <v>158629</v>
       </c>
       <c r="E12" s="13">
-        <v>305.8</v>
+        <v>261.5</v>
       </c>
       <c r="F12" s="12">
-        <v>2103</v>
+        <v>2408</v>
       </c>
       <c r="G12" s="12">
-        <v>112744</v>
+        <v>161037</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1172,25 +1169,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD1995C-42C9-513D-861B-8743FF29CB14}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
@@ -1212,13 +1214,31 @@
       <c r="G3" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -1226,22 +1246,40 @@
       <c r="D4" s="14">
         <v>43346</v>
       </c>
-      <c r="E4">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>19</v>
-      </c>
-      <c r="G4" s="10">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E4" s="14">
+        <v>44441</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1383</v>
+      </c>
+      <c r="G4" s="8">
+        <v>107</v>
+      </c>
+      <c r="H4" s="8">
+        <v>31</v>
+      </c>
+      <c r="I4" s="8">
+        <v>160</v>
+      </c>
+      <c r="J4" s="15">
+        <v>3.334</v>
+      </c>
+      <c r="K4" s="16">
+        <v>103.4</v>
+      </c>
+      <c r="L4" s="16">
+        <v>56.6</v>
+      </c>
+      <c r="M4" s="10">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
@@ -1249,22 +1287,40 @@
       <c r="D5" s="14">
         <v>43710</v>
       </c>
-      <c r="E5">
-        <v>162</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="14">
+        <v>44805</v>
+      </c>
+      <c r="F5" s="8">
+        <v>2245</v>
+      </c>
+      <c r="G5" s="8">
         <v>180</v>
       </c>
-      <c r="G5" s="10">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="8">
+        <v>57</v>
+      </c>
+      <c r="I5" s="8">
+        <v>281</v>
+      </c>
+      <c r="J5" s="15">
+        <v>3.404</v>
+      </c>
+      <c r="K5" s="16">
+        <v>194</v>
+      </c>
+      <c r="L5" s="16">
+        <v>87</v>
+      </c>
+      <c r="M5" s="10">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
@@ -1272,22 +1328,40 @@
       <c r="D6" s="14">
         <v>44445</v>
       </c>
-      <c r="E6">
-        <v>43</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="14">
+        <v>45540</v>
+      </c>
+      <c r="F6" s="8">
+        <v>5051</v>
+      </c>
+      <c r="G6" s="8">
+        <v>470</v>
+      </c>
+      <c r="H6" s="8">
+        <v>140</v>
+      </c>
+      <c r="I6" s="8">
+        <v>746</v>
+      </c>
+      <c r="J6" s="15">
+        <v>3.829</v>
+      </c>
+      <c r="K6" s="16">
+        <v>536</v>
+      </c>
+      <c r="L6" s="16">
+        <v>210</v>
+      </c>
+      <c r="M6" s="10">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
         <v>53</v>
-      </c>
-      <c r="G6" s="10">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -1295,22 +1369,40 @@
       <c r="D7" s="14">
         <v>44627</v>
       </c>
-      <c r="E7">
-        <v>81</v>
-      </c>
-      <c r="F7">
-        <v>109</v>
-      </c>
-      <c r="G7" s="10">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" s="14">
+        <v>45722</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1982</v>
+      </c>
+      <c r="G7" s="8">
+        <v>193</v>
+      </c>
+      <c r="H7" s="8">
+        <v>58</v>
+      </c>
+      <c r="I7" s="8">
+        <v>305</v>
+      </c>
+      <c r="J7" s="15">
+        <v>3.777</v>
+      </c>
+      <c r="K7" s="16">
+        <v>219.1</v>
+      </c>
+      <c r="L7" s="16">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="M7" s="10">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
@@ -1318,22 +1410,40 @@
       <c r="D8" s="14">
         <v>44809</v>
       </c>
-      <c r="E8">
-        <v>41</v>
-      </c>
-      <c r="F8">
-        <v>48</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" s="14">
+        <v>45904</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1942</v>
+      </c>
+      <c r="G8" s="8">
+        <v>194</v>
+      </c>
+      <c r="H8" s="8">
+        <v>65</v>
+      </c>
+      <c r="I8" s="8">
+        <v>312</v>
+      </c>
+      <c r="J8" s="15">
+        <v>3.565</v>
+      </c>
+      <c r="K8" s="16">
+        <v>231.7</v>
+      </c>
+      <c r="L8" s="16">
+        <v>80.3</v>
+      </c>
+      <c r="M8" s="10">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -1341,22 +1451,40 @@
       <c r="D9" s="14">
         <v>45173</v>
       </c>
-      <c r="E9">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>34</v>
-      </c>
-      <c r="G9" s="10">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" s="14">
+        <v>46265</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1414</v>
+      </c>
+      <c r="G9" s="8">
+        <v>140</v>
+      </c>
+      <c r="H9" s="8">
+        <v>56</v>
+      </c>
+      <c r="I9" s="8">
+        <v>229</v>
+      </c>
+      <c r="J9" s="15">
+        <v>3.137</v>
+      </c>
+      <c r="K9" s="16">
+        <v>175.6</v>
+      </c>
+      <c r="L9" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="M9" s="10">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
@@ -1364,199 +1492,138 @@
       <c r="D10" s="14">
         <v>45537</v>
       </c>
-      <c r="E10">
-        <v>55</v>
-      </c>
-      <c r="F10">
+      <c r="E10" s="14">
+        <v>46265</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1332</v>
+      </c>
+      <c r="G10" s="8">
+        <v>147</v>
+      </c>
+      <c r="H10" s="8">
+        <v>59</v>
+      </c>
+      <c r="I10" s="8">
+        <v>177</v>
+      </c>
+      <c r="J10" s="15">
+        <v>2.074</v>
+      </c>
+      <c r="K10" s="16">
+        <v>122.3</v>
+      </c>
+      <c r="L10" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="M10" s="10">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="12">
+        <v>15349</v>
+      </c>
+      <c r="G11" s="12">
+        <v>1431</v>
+      </c>
+      <c r="L11" s="17">
+        <v>627.8</v>
+      </c>
+      <c r="M11" s="18">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="10">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="11">
-        <v>431</v>
-      </c>
-      <c r="F11" s="11">
-        <v>505</v>
-      </c>
-      <c r="G11" s="15">
-        <v>1.172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1.94</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G14" s="10">
-        <v>4.38</v>
-      </c>
-      <c r="H14" s="10">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="10">
-        <v>3.34</v>
-      </c>
-      <c r="F15" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="G15" s="10">
-        <v>5.98</v>
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="14">
+        <v>46266</v>
+      </c>
+      <c r="F15" s="8">
+        <v>4537</v>
+      </c>
+      <c r="G15" s="9">
+        <v>185.6</v>
       </c>
       <c r="H15" s="10">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9.15</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="10">
-        <v>6.1</v>
-      </c>
-      <c r="F16" s="10">
-        <v>2.33</v>
-      </c>
-      <c r="G16" s="10">
-        <v>13.9</v>
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>46266</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1857</v>
+      </c>
+      <c r="G16" s="9">
+        <v>76</v>
       </c>
       <c r="H16" s="10">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="16">
-        <v>1.172</v>
-      </c>
-      <c r="F17" s="16">
-        <v>1.03</v>
-      </c>
-      <c r="G17" s="16">
-        <v>1.346</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="14">
-        <v>46266</v>
-      </c>
-      <c r="E20">
-        <v>52</v>
-      </c>
-      <c r="F20" s="9">
-        <v>60.9</v>
-      </c>
-      <c r="G20" s="10">
-        <v>6.5</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+        <v>9.35</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14">
-        <v>46266</v>
-      </c>
-      <c r="E21">
-        <v>209</v>
-      </c>
-      <c r="F21" s="9">
-        <v>244.9</v>
-      </c>
-      <c r="G21" s="10">
-        <v>6.97</v>
-      </c>
-      <c r="H21" s="9">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1578,7 +1645,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.25">
@@ -1586,16 +1653,16 @@
         <v>15</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1603,16 +1670,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="8">
-        <v>2323</v>
+        <v>3443</v>
       </c>
       <c r="C4" s="8">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D4" s="8">
-        <v>14000</v>
+        <v>19280</v>
       </c>
       <c r="E4" s="8">
-        <v>1940</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1620,16 +1687,16 @@
         <v>26</v>
       </c>
       <c r="B5" s="8">
-        <v>3448</v>
+        <v>3194</v>
       </c>
       <c r="C5" s="8">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="D5" s="8">
-        <v>20680</v>
+        <v>18950</v>
       </c>
       <c r="E5" s="8">
-        <v>2410</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1637,16 +1704,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="8">
-        <v>1713</v>
+        <v>2128</v>
       </c>
       <c r="C6" s="8">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="D6" s="8">
-        <v>10860</v>
+        <v>12350</v>
       </c>
       <c r="E6" s="8">
-        <v>1310</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1654,16 +1721,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="8">
-        <v>702</v>
+        <v>2783</v>
       </c>
       <c r="C7" s="8">
-        <v>68</v>
+        <v>255</v>
       </c>
       <c r="D7" s="8">
-        <v>4730</v>
+        <v>18110</v>
       </c>
       <c r="E7" s="8">
-        <v>750</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1671,16 +1738,16 @@
         <v>28</v>
       </c>
       <c r="B8" s="8">
-        <v>717</v>
+        <v>3680</v>
       </c>
       <c r="C8" s="8">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="D8" s="8">
-        <v>4850</v>
+        <v>21770</v>
       </c>
       <c r="E8" s="8">
-        <v>650</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1688,16 +1755,16 @@
         <v>29</v>
       </c>
       <c r="B9" s="8">
-        <v>1996</v>
+        <v>2180</v>
       </c>
       <c r="C9" s="8">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D9" s="8">
-        <v>10830</v>
+        <v>12200</v>
       </c>
       <c r="E9" s="8">
-        <v>1710</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1705,16 +1772,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="8">
-        <v>2729</v>
+        <v>1838</v>
       </c>
       <c r="C10" s="8">
-        <v>252</v>
+        <v>158</v>
       </c>
       <c r="D10" s="8">
-        <v>18040</v>
+        <v>11800</v>
       </c>
       <c r="E10" s="8">
-        <v>2950</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,26 +1789,26 @@
         <v>30</v>
       </c>
       <c r="B11" s="8">
-        <v>1781</v>
+        <v>2927</v>
       </c>
       <c r="C11" s="8">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="D11" s="8">
-        <v>10340</v>
+        <v>16980</v>
       </c>
       <c r="E11" s="8">
-        <v>1380</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1760,71 +1827,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B6" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B8" s="20" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
